--- a/DW3_QM33_SDK_1.1.1/outputs/uwb_interval_summary_20260930/uwb_点对点通信统计.xlsx
+++ b/DW3_QM33_SDK_1.1.1/outputs/uwb_interval_summary_20260930/uwb_点对点通信统计.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试结果" sheetId="1" r:id="R8e7f4d31a01c4b4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试结果" sheetId="1" r:id="R80b68e722ed4495b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -370,15 +370,15 @@
         <x:v>299822</x:v>
       </x:c>
       <x:c r="D2" s="13" t="n">
-        <x:v>489</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E2" s="14" t="n">
         <x:f>D2/B2</x:f>
-        <x:v>0.00163</x:v>
+        <x:v>0.0005933333333333333</x:v>
       </x:c>
       <x:c r="F2" s="15" t="n">
         <x:f>1-E2</x:f>
-        <x:v>0.99837</x:v>
+        <x:v>0.9994066666666667</x:v>
       </x:c>
       <x:c r="G2" s="10" t="str">
         <x:v>50分03.870秒</x:v>
@@ -395,15 +395,15 @@
         <x:v>299905</x:v>
       </x:c>
       <x:c r="D3" s="13" t="n">
-        <x:v>191</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E3" s="14" t="n">
         <x:f>D3/B3</x:f>
-        <x:v>0.0006366666666666667</x:v>
+        <x:v>0.00031666666666666665</x:v>
       </x:c>
       <x:c r="F3" s="15" t="n">
         <x:f>1-E3</x:f>
-        <x:v>0.9993633333333334</x:v>
+        <x:v>0.9996833333333334</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
         <x:v>26分33.919秒</x:v>
@@ -420,15 +420,15 @@
         <x:v>299888</x:v>
       </x:c>
       <x:c r="D4" s="13" t="n">
-        <x:v>225</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E4" s="14" t="n">
         <x:f>D4/B4</x:f>
-        <x:v>0.00075</x:v>
+        <x:v>0.0003733333333333333</x:v>
       </x:c>
       <x:c r="F4" s="15" t="n">
         <x:f>1-E4</x:f>
-        <x:v>0.99925</x:v>
+        <x:v>0.9996266666666667</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
         <x:v>21分39.105秒</x:v>
@@ -445,15 +445,15 @@
         <x:v>299914</x:v>
       </x:c>
       <x:c r="D5" s="13" t="n">
-        <x:v>175</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E5" s="14" t="n">
         <x:f>D5/B5</x:f>
-        <x:v>0.0005833333333333334</x:v>
+        <x:v>0.0002866666666666667</x:v>
       </x:c>
       <x:c r="F5" s="15" t="n">
         <x:f>1-E5</x:f>
-        <x:v>0.9994166666666666</x:v>
+        <x:v>0.9997133333333333</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
         <x:v>16分43.817秒</x:v>
@@ -470,15 +470,15 @@
         <x:v>299866</x:v>
       </x:c>
       <x:c r="D6" s="13" t="n">
-        <x:v>269</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E6" s="14" t="n">
         <x:f>D6/B6</x:f>
-        <x:v>0.0008966666666666667</x:v>
+        <x:v>0.00044666666666666666</x:v>
       </x:c>
       <x:c r="F6" s="15" t="n">
         <x:f>1-E6</x:f>
-        <x:v>0.9991033333333333</x:v>
+        <x:v>0.9995533333333333</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
         <x:v>11分46.987秒</x:v>
@@ -495,15 +495,15 @@
         <x:v>299896</x:v>
       </x:c>
       <x:c r="D7" s="13" t="n">
-        <x:v>210</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E7" s="14" t="n">
         <x:f>D7/B7</x:f>
-        <x:v>0.0007</x:v>
+        <x:v>0.00034666666666666667</x:v>
       </x:c>
       <x:c r="F7" s="15" t="n">
         <x:f>1-E7</x:f>
-        <x:v>0.9993</x:v>
+        <x:v>0.9996533333333333</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
         <x:v>6分52.440秒</x:v>
@@ -511,7 +511,7 @@
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="18" t="str">
-        <x:v>口径：丢包+错误数 = lost + phy_err + invalid；成功率 = (发送数 − 失败数) / 发送数。</x:v>
+        <x:v>计数口径：按包统计失败数 = lost + invalid（本批 invalid=0）；成功率 = (发送数 − 失败数) / 发送数。</x:v>
       </x:c>
       <x:c r="B9" s="18"/>
       <x:c r="C9" s="18"/>
@@ -522,7 +522,7 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="18" t="str">
-        <x:v>注意：phy_err 可能与 lost 对应同一丢失数据包；按要求直接相加可能重复计数。</x:v>
+        <x:v>phy_err 仅作诊断，不叠加进失败包数；各轮事件数（10/5/4/3/2/1 ms）= 311/96/113/89/135/106，可能与 lost 重叠。</x:v>
       </x:c>
       <x:c r="B10" s="18"/>
       <x:c r="C10" s="18"/>
